--- a/帝国时代2决定版 文明联盟 城堡流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 城堡流最优研究顺序 By RemonBo.xlsx
@@ -20,9 +20,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·城堡本体强化'!$A$1:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·城堡本体强化'!$A$1:$E$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·城堡本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·石料与前置'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·石料与前置'!$A$1:$E$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·石料与前置'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与城堡流无关·可跳过'!$A$1:$D$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与城堡流无关·可跳过'!$1:$1</definedName>
@@ -1410,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1448,9 +1448,9 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1475,9 +1475,9 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1501,165 +1501,165 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>撒克逊人</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>塔/城堡城堡起基础箭+100%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>基础箭数提升，塔与城堡的输出直接上一个台阶</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>塔/城堡城堡起基础箭+100%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>穿透伤害，对高护甲目标有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>城堡可用攻城工程技师</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>直接强化城堡</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>加固堡垒（防御工事每分钟回500生命）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>穿透伤害，对高护甲目标有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>持续回血，长期更省维修成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>土堡（团队城堡工作速度+25%）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>城堡可用攻城工程技师</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>直接强化城堡</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>加固堡垒（防御工事每分钟回500生命）</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>土堡（团队城堡工作速度+25%）</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>建造/工作效率提升</t>
+          <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>A</t>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>人口容量提升</t>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -1740,14 +1740,14 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>直接强化城堡</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1767,14 +1767,14 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>直接强化城堡</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1806,103 +1806,103 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害，正面更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>直接强化城堡</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>图皮</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>附加中毒伤害</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>图皮</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>塔楼和城堡提供的人口空间 +10</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -1914,76 +1914,76 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>马普切</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>敌方城堡始终可见</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>直接强化城堡</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>直接强化城堡</t>
+          <t>情报优势：始终能掌握对方动向</t>
         </is>
       </c>
     </row>
@@ -1995,27 +1995,54 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22"/>
+  <autoFilter ref="A1:E23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2027,7 +2054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2065,56 +2092,56 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>撒克逊人</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>攻城/防御工事升级木材-75%，研究+100%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>直接强化城堡</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2153,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2141,24 +2168,24 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2168,51 +2195,51 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>免费获得，等于直接省下这笔支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>城堡城堡/帝王费用-15/25%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>免费获得，等于直接省下这笔支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>城堡城堡/帝王费用-15/25%</t>
+          <t>重装骑射手城堡可升级，成本-50%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2222,66 +2249,39 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>城墙费用 -50%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>重装骑射手城堡可升级，成本-50%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>城墙费用 -50%</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/帝国时代2决定版 文明联盟 城堡流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 城堡流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·城堡本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·石料与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与城堡流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·城堡本体强化'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·城堡本体强化'!$A$1:$E$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·城堡本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·石料与前置'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·石料与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与城堡流无关·可跳过'!$A$1:$D$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与城堡流无关·可跳过'!$A$1:$D$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与城堡流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -574,7 +574,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>第 1 位</t>
@@ -592,7 +592,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 15/21；缺 工兵、砖石建筑、建筑学、开垛口；最直接一条：建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 工兵、砖石建筑、建筑学、开垛口；最直接一条：建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
         </is>
       </c>
     </row>
@@ -606,11 +606,11 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 3 / 弱 0）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：高海拔单位和建筑受伤-15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 5 条（强 3 / 弱 1）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：高海拔单位和建筑受伤-15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；城堡科技树 17/21；缺 建筑学、开垛口、炮塔、护腕；最直接一条：堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 建筑学、开垛口、炮塔、护腕；最直接一条：堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 19/21；缺 建筑学、护腕；最直接一条：开垛口（城堡射程+3；驻扎的步兵射箭）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 19/21；缺 建筑学、护腕；最直接一条：开垛口（城堡射程+3；驻扎的步兵射箭）</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 3 / 弱 0）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：城堡可用攻城工程技师</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：城堡可用攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -670,13 +670,13 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔（备选）</t>
+          <t>保加利亚（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>每控制一个TC/城堡步兵花费-5%（最多-20%）；塔/城堡城堡起基础箭+100%</t>
+          <t>塔/城堡城堡起基础箭+100%</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场；最直接一条：每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场；最直接一条：每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
         </is>
       </c>
     </row>
@@ -712,27 +712,27 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫（备选）</t>
+          <t>西西里（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；城堡科技树 14/21；缺 建筑学、箭孔、开垛口、灼热箭；最直接一条：罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>保加利亚（备选）</t>
+          <t>波斯（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
+          <t>高海拔单位和建筑受伤-15%；斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 3 / 弱 0）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：高海拔单位和建筑受伤-15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 1）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：高海拔单位和建筑受伤-15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>5</v>
       </c>
@@ -853,7 +853,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 17/21；缺 建筑学、开垛口、炮塔、护腕；最直接一条：堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 建筑学、开垛口、炮塔、护腕；最直接一条：堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：城堡可用攻城工程技师</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：城堡可用攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>土堡（团队城堡工作速度+25%）</t>
+          <t>城堡时代可建营垒</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）；军事建筑 (城堡除外) 提供的人口空间 +5</t>
+          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%；初始石料+100</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；城堡科技树 14/21；缺 建筑学、箭孔、开垛口、灼热箭；最直接一条：罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>城堡时代可建营垒</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%</t>
+          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 12/21；缺 工兵、建筑学、箭孔、开垛口；最直接一条：斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1033,17 +1033,17 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 砖石建筑、建筑学、强化城墙、开垛口；最直接一条：箭毒（步弓手/防御工事造成中毒伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 12/21；缺 工兵、建筑学、箭孔、开垛口；最直接一条：斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 11/21；缺 工兵、砖石建筑、建筑学、强化城墙；最直接一条：伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1083,27 +1083,27 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
+          <t>任何高地可建除TC外所有建筑；迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）；建筑的视野 +3</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；城堡科技树 14/21；缺 砖石建筑、建筑学、强化城墙、开垛口；最直接一条：箭毒（步弓手/防御工事造成中毒伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 4 / 弱 0）；城堡科技树 14/21；缺 工兵、开垛口、弹道学、灼热箭；最直接一条：任何高地可建除TC外所有建筑</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>敌方城堡始终可见</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 11/21；缺 工兵、砖石建筑、建筑学、强化城墙；最直接一条：伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 17/21；缺 强化城墙、开垛口、灼热箭、护腕；最直接一条：敌方城堡始终可见</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+          <t>建筑石料-15%</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 4 / 弱 0）；城堡科技树 14/21；缺 工兵、开垛口、弹道学、灼热箭；最直接一条：任何高地可建除TC外所有建筑</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；城堡科技树 18/21；缺 建筑学、开垛口、炮塔；最直接一条：建筑石料-15%</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>敌方城堡始终可见；布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；城堡科技树 17/21；缺 强化城墙、开垛口、灼热箭、护腕；最直接一条：敌方城堡始终可见</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；城堡科技树 18/21；缺 囤积、开垛口、攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,27 +1203,27 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车；库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
+          <t>哨站视野 +3 且不消耗石料</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；城堡科技树 13/21；缺 建筑学、强化城墙、箭孔、开垛口；最直接一条：封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；城堡科技树 17/21；缺 囤积、箭孔、开垛口、炮塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="51" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>城堡城堡/帝王费用-15/25%</t>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 16/21；缺 开垛口、灼热箭、炮塔、护腕；最直接一条：城堡城堡/帝王费用-15/25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 建筑学、箭孔、开垛口、灼热箭；最直接一条：罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>建筑石料-15%</t>
+          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 1）；城堡科技树 18/21；缺 建筑学、开垛口、炮塔；最直接一条：建筑石料-15%</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 13/21；缺 建筑学、强化城墙、箭孔、开垛口；最直接一条：库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>重装骑射手城堡可升级，成本-50%</t>
+          <t>城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 15/21；缺 囤积、工兵、建筑学、箭孔；最直接一条：重装骑射手城堡可升级，成本-50%</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 16/21；缺 开垛口、灼热箭、炮塔、护腕；最直接一条：城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）</t>
+          <t>城墙费用 -50%</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；城堡科技树 18/21；缺 囤积、开垛口、攻城工程技师</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；城堡科技树 17/21；缺 箭孔、开垛口、炮塔、攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>城墙费用 -50%</t>
+          <t>城堡起TC木材费用-50%</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；城堡科技树 17/21；缺 箭孔、开垛口、炮塔、攻城工程技师</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>哨站视野 +3 且不消耗石料</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1393,12 +1393,42 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；城堡科技树 17/21；缺 囤积、箭孔、开垛口、炮塔</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 囤积、箭孔、开垛口</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>土堡（团队城堡工作速度+25%）</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>城堡时代起</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F21"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1410,7 +1440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1541,17 +1571,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
+          <t>高海拔单位和建筑受伤-15%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>穿透伤害，对高护甲目标有效</t>
+          <t>减少受到的伤害，正面更耐打</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1593,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1578,7 +1608,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>穿透伤害，对高护甲目标有效</t>
         </is>
       </c>
     </row>
@@ -1590,22 +1620,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>城堡可用攻城工程技师</t>
+          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>提前解锁，抢一个时代的节奏</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1652,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>加固堡垒（防御工事每分钟回500生命）</t>
+          <t>城堡可用攻城工程技师</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>持续回血，长期更省维修成本</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -1644,22 +1674,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>土堡（团队城堡工作速度+25%）</t>
+          <t>攻城/防御工事升级木材-75%，研究+100%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>工作速度提升，成型更快</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1701,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+          <t>加固堡垒（防御工事每分钟回500生命）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1686,115 +1716,115 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>持续回血，长期更省维修成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>城堡时代可建营垒</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>黑暗可建城楼（替瞭望塔系）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>防御工事建造+50%，TC建造+100%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>建造/工作效率提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>初始石料+100</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>军事建筑 (城堡除外) 提供的人口空间 +5</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>城堡时代可建营垒</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>黑暗可建城楼（替瞭望塔系）</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>防御工事建造+50%，TC建造+100%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>建造/工作效率提升</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1909,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -1887,22 +1917,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>塔楼和城堡提供的人口空间 +10</t>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+          <t>额外产出资源，经济滚雪球更快</t>
         </is>
       </c>
     </row>
@@ -1914,49 +1944,49 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>任何高地可建除TC外所有建筑</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
         </is>
       </c>
     </row>
@@ -1968,22 +1998,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>敌方城堡始终可见</t>
+          <t>建筑的视野 +3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>情报优势：始终能掌握对方动向</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -1995,12 +2025,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+          <t>敌方城堡始终可见</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2010,39 +2040,93 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>提前解锁，抢一个时代的节奏</t>
+          <t>情报优势：始终能掌握对方动向</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>建筑石料-15%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>哨站视野 +3 且不消耗石料</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2054,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2119,169 +2203,385 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>撒克逊人</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>建筑修理费用 -25%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>TC石料费用-50%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>塔楼和城堡提供的人口空间 +10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>马普切</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>军事建筑 (城堡除外) 提供的人口空间 +5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>库曼</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>免费获得，等于直接省下这笔支出</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>法兰克</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>重装骑射手城堡可升级，成本-50%</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>城墙费用 -50%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>城堡起TC木材费用-50%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>城墙费用 -50%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>土堡（团队城堡工作速度+25%）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2293,7 +2593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2415,12 +2715,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>步弓手文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2430,19 +2730,19 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骑射手文明</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2452,19 +2752,19 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>骑射手文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2474,19 +2774,19 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>防御和海军文明</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -2496,19 +2796,19 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>防御和海军文明</t>
+          <t>攻城武器和大象文明</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2518,19 +2818,19 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -2540,19 +2840,19 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骑兵和僧侣文明</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2562,19 +2862,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2584,19 +2884,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>海军文明</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2606,19 +2906,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>海军文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2628,19 +2928,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2650,19 +2950,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>骑射手文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2672,19 +2972,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>骑射手文明</t>
+          <t>象兵和海军文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2694,19 +2994,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>象兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2716,19 +3016,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵与僧侣文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2738,19 +3038,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2760,19 +3060,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牧场取代农田」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>海军和火药文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2782,19 +3082,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2804,19 +3104,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骆驼和海军文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2826,19 +3126,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>骆驼和海军文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2848,19 +3148,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>骆驼和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「市场贸易税仅5%」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2870,19 +3170,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2892,19 +3192,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2914,19 +3214,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2936,19 +3236,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2958,19 +3258,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2980,19 +3280,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3002,19 +3302,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3024,19 +3324,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3046,19 +3346,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3068,19 +3368,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3090,19 +3390,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「开局显示敌方TC」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3112,19 +3412,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「开局显示敌方TC」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3134,19 +3434,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「高地受伤-10%」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3156,34 +3456,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「高地受伤-10%」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强城堡</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D40"/>
+  <autoFilter ref="A1:D39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3328,7 +3606,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 3）；城堡科技树 18/21。缺：开垛口、灼热箭、炮塔</t>
+          <t>原生条目 2 条（强 3）；城堡科技树 18/21。缺：开垛口、灼热箭、炮塔</t>
         </is>
       </c>
     </row>
@@ -3382,28 +3660,28 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17/21</t>
+          <t>16/21</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>土堡（团队城堡工作速度+25%）</t>
+          <t>城堡时代可建营垒</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；城堡科技树 17/21。缺：工兵、建筑学、开垛口、炮塔</t>
+          <t>原生条目 2 条（强 1）；城堡科技树 16/21。缺：囤积、强化城墙、箭孔、开垛口、炮塔</t>
         </is>
       </c>
     </row>
@@ -3413,22 +3691,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14/21</t>
+          <t>17/21</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）；军事建筑 (城堡除外) 提供的人口空间 +5</t>
+          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；城堡科技树 14/21。缺：建筑学、箭孔、开垛口、灼热箭、炮塔</t>
+          <t>原生条目 3 条（强 2）；城堡科技树 17/21。缺：建筑学、强化城墙、开垛口、炮塔</t>
         </is>
       </c>
     </row>
@@ -3438,22 +3716,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16/21</t>
+          <t>15/21</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>城堡时代可建营垒</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；城堡科技树 16/21。缺：囤积、强化城墙、箭孔、开垛口、炮塔</t>
+          <t>原生条目 1 条（强 1）；城堡科技树 15/21。缺：强化城墙、箭孔、开垛口、炮塔、攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -3463,22 +3741,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17/21</t>
+          <t>12/21</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%</t>
+          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；城堡科技树 17/21。缺：建筑学、强化城墙、开垛口、炮塔</t>
+          <t>原生条目 1 条（强 1）；城堡科技树 12/21。缺：工兵、建筑学、箭孔、开垛口、弹道学</t>
         </is>
       </c>
     </row>
@@ -3488,22 +3766,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15/21</t>
+          <t>14/21</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；城堡科技树 15/21。缺：强化城墙、箭孔、开垛口、炮塔、攻城工程技师</t>
+          <t>原生条目 2 条（强 2）；城堡科技树 14/21。缺：砖石建筑、建筑学、强化城墙、开垛口、炮塔</t>
         </is>
       </c>
     </row>
@@ -3513,22 +3791,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12/21</t>
+          <t>11/21</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；城堡科技树 12/21。缺：工兵、建筑学、箭孔、开垛口、弹道学</t>
+          <t>原生条目 1 条（强 1）；城堡科技树 11/21。缺：工兵、砖石建筑、建筑学、强化城墙、箭孔</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3816,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3548,12 +3826,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
+          <t>任何高地可建除TC外所有建筑；堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；城堡科技树 14/21。缺：砖石建筑、建筑学、强化城墙、开垛口、炮塔</t>
+          <t>原生条目 1 条（强 4）；城堡科技树 14/21。缺：工兵、开垛口、弹道学、灼热箭、化学</t>
         </is>
       </c>
     </row>
@@ -3563,47 +3841,47 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11/21</t>
+          <t>17/21</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>敌方城堡始终可见；布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；城堡科技树 11/21。缺：工兵、砖石建筑、建筑学、强化城墙、箭孔</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 2）；城堡科技树 17/21。缺：强化城墙、开垛口、灼热箭、护腕</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14/21</t>
+          <t>18/21</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>任何高地可建除TC外所有建筑；堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+          <t>建筑石料-15%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 4）；城堡科技树 14/21。缺：工兵、开垛口、弹道学、灼热箭、化学</t>
+          <t>原生条目 1 条（强 1）；城堡科技树 18/21。缺：建筑学、开垛口、炮塔</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3941,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -3689,7 +3967,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 15/21；缺 工兵、砖石建筑、建筑学、开垛口；最直接一条：建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 工兵、砖石建筑、建筑学、开垛口；最直接一条：建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
         </is>
       </c>
     </row>
@@ -3719,11 +3997,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 19/21；缺 建筑学、护腕；最直接一条：开垛口（城堡射程+3；驻扎的步兵射箭）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 19/21；缺 建筑学、护腕；最直接一条：开垛口（城堡射程+3；驻扎的步兵射箭）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -3744,12 +4022,12 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>每控制一个TC/城堡步兵花费-5%（最多-20%）；塔/城堡城堡起基础箭+100%</t>
+          <t>塔/城堡城堡起基础箭+100%</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场；最直接一条：每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场；最直接一条：每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
         </is>
       </c>
     </row>
@@ -3774,16 +4052,16 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
+          <t>高海拔单位和建筑受伤-15%；斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 3 / 弱 0）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：高海拔单位和建筑受伤-15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 1）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：高海拔单位和建筑受伤-15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -3809,7 +4087,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 17/21；缺 建筑学、开垛口、炮塔、护腕；最直接一条：堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 建筑学、开垛口、炮塔、护腕；最直接一条：堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
         </is>
       </c>
     </row>
@@ -3839,7 +4117,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：城堡可用攻城工程技师</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；城堡科技树 18/21；缺 开垛口、灼热箭、炮塔；最直接一条：城堡可用攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -3849,7 +4127,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3864,12 +4142,12 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>土堡（团队城堡工作速度+25%）</t>
+          <t>城堡时代可建营垒</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
         </is>
       </c>
     </row>
@@ -3879,7 +4157,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3894,22 +4172,22 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）；军事建筑 (城堡除外) 提供的人口空间 +5</t>
+          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%；初始石料+100</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；城堡科技树 14/21；缺 建筑学、箭孔、开垛口、灼热箭；最直接一条：罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3924,22 +4202,22 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>城堡时代可建营垒</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3954,12 +4232,12 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%</t>
+          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 12/21；缺 工兵、建筑学、箭孔、开垛口；最直接一条：斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
     </row>
@@ -3969,7 +4247,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -3984,22 +4262,22 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 砖石建筑、建筑学、强化城墙、开垛口；最直接一条：箭毒（步弓手/防御工事造成中毒伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4014,22 +4292,22 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 12/21；缺 工兵、建筑学、箭孔、开垛口；最直接一条：斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 11/21；缺 工兵、砖石建筑、建筑学、强化城墙；最直接一条：伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4044,22 +4322,22 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
+          <t>任何高地可建除TC外所有建筑；迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）；建筑的视野 +3</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；城堡科技树 14/21；缺 砖石建筑、建筑学、强化城墙、开垛口；最直接一条：箭毒（步弓手/防御工事造成中毒伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 4 / 弱 0）；城堡科技树 14/21；缺 工兵、开垛口、弹道学、灼热箭；最直接一条：任何高地可建除TC外所有建筑</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4074,12 +4352,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>敌方城堡始终可见</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 11/21；缺 工兵、砖石建筑、建筑学、强化城墙；最直接一条：伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 17/21；缺 强化城墙、开垛口、灼热箭、护腕；最直接一条：敌方城堡始终可见</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4367,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4104,12 +4382,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+          <t>建筑石料-15%</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 4 / 弱 0）；城堡科技树 14/21；缺 工兵、开垛口、弹道学、灼热箭；最直接一条：任何高地可建除TC外所有建筑</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；城堡科技树 18/21；缺 建筑学、开垛口、炮塔；最直接一条：建筑石料-15%</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4397,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4134,12 +4412,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>敌方城堡始终可见；布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；城堡科技树 17/21；缺 强化城墙、开垛口、灼热箭、护腕；最直接一条：敌方城堡始终可见</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；城堡科技树 18/21；缺 囤积、开垛口、攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4427,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -4164,22 +4442,22 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车；库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
+          <t>哨站视野 +3 且不消耗石料</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；城堡科技树 13/21；缺 建筑学、强化城墙、箭孔、开垛口；最直接一条：封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；城堡科技树 17/21；缺 囤积、箭孔、开垛口、炮塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="51" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4194,22 +4472,22 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>城堡城堡/帝王费用-15/25%</t>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 16/21；缺 开垛口、灼热箭、炮塔、护腕；最直接一条：城堡城堡/帝王费用-15/25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 建筑学、箭孔、开垛口、灼热箭；最直接一条：罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -4224,12 +4502,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>建筑石料-15%</t>
+          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 1）；城堡科技树 18/21；缺 建筑学、开垛口、炮塔；最直接一条：建筑石料-15%</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 13/21；缺 建筑学、强化城墙、箭孔、开垛口；最直接一条：库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4517,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -4254,12 +4532,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>重装骑射手城堡可升级，成本-50%</t>
+          <t>城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；城堡科技树 15/21；缺 囤积、工兵、建筑学、箭孔；最直接一条：重装骑射手城堡可升级，成本-50%</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 16/21；缺 开垛口、灼热箭、炮塔、护腕；最直接一条：城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4547,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -4284,12 +4562,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）</t>
+          <t>城墙费用 -50%</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；城堡科技树 18/21；缺 囤积、开垛口、攻城工程技师</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；城堡科技树 17/21；缺 箭孔、开垛口、炮塔、攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4577,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -4314,12 +4592,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>城墙费用 -50%</t>
+          <t>城堡起TC木材费用-50%</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；城堡科技树 17/21；缺 箭孔、开垛口、炮塔、攻城工程技师</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4607,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -4344,12 +4622,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>哨站视野 +3 且不消耗石料</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；城堡科技树 17/21；缺 囤积、箭孔、开垛口、炮塔</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 囤积、箭孔、开垛口</t>
         </is>
       </c>
     </row>
@@ -4359,27 +4637,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强城堡</t>
+          <t>土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4667,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -4409,7 +4687,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4697,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -4439,7 +4717,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4727,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -4469,7 +4747,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4757,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -4499,7 +4777,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -4959,7 +5237,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -4979,7 +5257,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牧场取代农田」）</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5679,101 +5957,141 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>① 只看直接作用于城堡本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与城堡流无关·可跳过」）；</t>
+          <t>直接加强城堡本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（建筑与防御工事）生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="12" t="inlineStr"/>
-      <c r="B17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与城堡流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="12" t="inlineStr"/>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B20" s="12" t="inlineStr"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 城堡流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 城堡流最优研究顺序 By RemonBo.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·城堡本体强化'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·城堡本体强化'!$A$1:$E$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·城堡本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与城堡流无关·可跳过'!$A$1:$D$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与城堡流无关·可跳过'!$A$1:$D$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与城堡流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -670,13 +670,13 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>保加利亚（备选）</t>
+          <t>柏柏尔（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
     </row>
@@ -712,27 +712,27 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>西西里（备选）</t>
+          <t>保加利亚（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>波斯（备选）</t>
+          <t>西西里（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>备选：阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>高海拔单位和建筑受伤-15%；斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
+          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
@@ -873,7 +873,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>城堡可用攻城工程技师；攻城/防御工事升级木材-75%，研究+100%；加固堡垒（防御工事每分钟回500生命）</t>
+          <t>城堡可用攻城工程技师；加固堡垒（防御工事每分钟回500生命）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>城堡时代可建营垒</t>
+          <t>土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%；初始石料+100</t>
+          <t>城堡时代可建营垒</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -963,17 +963,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 12/21；缺 工兵、建筑学、箭孔、开垛口；最直接一条：斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
+          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 砖石建筑、建筑学、强化城墙、开垛口；最直接一条：箭毒（步弓手/防御工事造成中毒伤害）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 12/21；缺 工兵、建筑学、箭孔、开垛口；最直接一条：斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 11/21；缺 工兵、砖石建筑、建筑学、强化城墙；最直接一条：伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 砖石建筑、建筑学、强化城墙、开垛口；最直接一条：箭毒（步弓手/防御工事造成中毒伤害）</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>任何高地可建除TC外所有建筑；迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）；建筑的视野 +3</t>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 4 / 弱 0）；城堡科技树 14/21；缺 工兵、开垛口、弹道学、灼热箭；最直接一条：任何高地可建除TC外所有建筑</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 11/21；缺 工兵、砖石建筑、建筑学、强化城墙；最直接一条：伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>敌方城堡始终可见</t>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点；任何高地可建除TC外所有建筑</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 17/21；缺 强化城墙、开垛口、灼热箭、护腕；最直接一条：敌方城堡始终可见</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 4 / 弱 0）；城堡科技树 14/21；缺 工兵、开垛口、弹道学、灼热箭；最直接一条：任何高地可建除TC外所有建筑</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,17 +1143,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>建筑石料-15%</t>
+          <t>敌方城堡始终可见</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；城堡科技树 18/21；缺 建筑学、开垛口、炮塔；最直接一条：建筑石料-15%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 17/21；缺 强化城墙、开垛口、灼热箭、护腕；最直接一条：敌方城堡始终可见</t>
         </is>
       </c>
     </row>
@@ -1187,13 +1187,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,17 +1203,17 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>哨站视野 +3 且不消耗石料</t>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；城堡科技树 17/21；缺 囤积、箭孔、开垛口、炮塔</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 14/21；缺 建筑学、箭孔、开垛口、灼热箭；最直接一条：罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 建筑学、箭孔、开垛口、灼热箭；最直接一条：罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="51" customHeight="1">
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 13/21；缺 建筑学、强化城墙、箭孔、开垛口；最直接一条：库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
+          <t>城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 13/21；缺 建筑学、强化城墙、箭孔、开垛口；最直接一条：库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 16/21；缺 开垛口、灼热箭、炮塔、护腕；最直接一条：城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>城堡城堡/帝王费用-15/25%</t>
+          <t>城堡起TC木材费用-50%</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 16/21；缺 开垛口、灼热箭、炮塔、护腕；最直接一条：城堡城堡/帝王费用-15/25%</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>城墙费用 -50%</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；城堡科技树 17/21；缺 箭孔、开垛口、炮塔、攻城工程技师</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 囤积、箭孔、开垛口</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>城堡起TC木材费用-50%</t>
+          <t>城墙费用 -50%</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；城堡科技树 17/21；缺 箭孔、开垛口、炮塔、攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>建筑石料-15%</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 囤积、箭孔、开垛口</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 1）；城堡科技树 18/21；缺 建筑学、开垛口、炮塔；最直接一条：建筑石料-15%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1413,22 +1413,52 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>土堡（团队城堡工作速度+25%）</t>
+          <t>建筑木材-15%</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 1）；城堡科技树 16/21；缺 箭孔、开垛口、炮塔、攻城工程技师；最直接一条：建筑木材-15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>哨站视野 +3 且不消耗石料</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>阶段3·资源效率；原生条目 1 条（强 0 / 弱 1）；城堡科技树 17/21；缺 囤积、箭孔、开垛口、炮塔</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F22"/>
+  <autoFilter ref="A1:F23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1440,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1679,17 +1709,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%</t>
+          <t>加固堡垒（防御工事每分钟回500生命）</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1731,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>加固堡垒（防御工事每分钟回500生命）</t>
+          <t>土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1716,7 +1746,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>持续回血，长期更省维修成本</t>
+          <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -1748,9 +1778,9 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1775,9 +1805,9 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1802,29 +1832,29 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>初始石料+100</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>减少受到的伤害，正面更耐打</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1866,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1851,7 +1881,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>减少受到的伤害，正面更耐打</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1893,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1878,11 +1908,11 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+          <t>附加中毒伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -1895,17 +1925,17 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
+          <t>塔楼和城堡提供的人口空间 +10</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>附加中毒伤害</t>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1993,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -1976,44 +2006,44 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
           <t>迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>建筑的视野 +3</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -2025,22 +2055,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>敌方城堡始终可见</t>
+          <t>建筑的视野 +3</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>情报优势：始终能掌握对方动向</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2082,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>建筑石料-15%</t>
+          <t>敌方城堡始终可见</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2067,7 +2097,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>情报优势：始终能掌握对方动向</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2128,8 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>哨站视野 +3 且不消耗石料</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E25"/>
+  <autoFilter ref="A1:E24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2138,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2264,49 +2267,49 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>攻城/防御工事升级木材-75%，研究+100%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>保加利亚</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>TC石料费用-50%</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>塔楼和城堡提供的人口空间 +10</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2321,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+          <t>初始石料+100</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2333,7 +2336,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>采集效率提升，经济成型更快</t>
+          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2394,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2399,22 +2402,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>军事建筑 (城堡除外) 提供的人口空间 +5</t>
+          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+          <t>免费获得，等于直接省下这笔支出</t>
         </is>
       </c>
     </row>
@@ -2426,22 +2429,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
+          <t>城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>免费获得，等于直接省下这笔支出</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -2453,12 +2456,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>城堡城堡/帝王费用-15/25%</t>
+          <t>城堡起TC木材费用-50%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2480,17 +2483,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>城墙费用 -50%</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -2507,17 +2510,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>城堡起TC木材费用-50%</t>
+          <t>城墙费用 -50%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2534,12 +2537,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>建筑石料-15%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2561,27 +2564,54 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>土堡（团队城堡工作速度+25%）</t>
+          <t>建筑木材-15%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>工作速度提升，成型更快</t>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>哨站视野 +3 且不消耗石料</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E16"/>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2593,7 +2623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2913,12 +2943,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2928,19 +2958,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>骑射手文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2950,19 +2980,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>骑射手文明</t>
+          <t>象兵和海军文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2972,19 +3002,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>象兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2994,19 +3024,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵与僧侣文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3016,19 +3046,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3038,19 +3068,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牧场取代农田」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3060,19 +3090,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牧场取代农田」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -3082,19 +3112,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骆驼和海军文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -3104,19 +3134,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>骆驼和海军文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3126,19 +3156,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>骆驼和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「市场贸易税仅5%」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -3148,19 +3178,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3170,19 +3200,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -3192,19 +3222,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -3214,19 +3244,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -3236,19 +3266,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -3258,19 +3288,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3280,19 +3310,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3302,19 +3332,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3324,19 +3354,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3346,19 +3376,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3368,19 +3398,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「开局显示敌方TC」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3390,19 +3420,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「开局显示敌方TC」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3412,19 +3442,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「高地受伤-10%」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3434,34 +3464,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「高地受伤-10%」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强城堡</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D39"/>
+  <autoFilter ref="A1:D38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3660,28 +3668,28 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16/21</t>
+          <t>17/21</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>城堡时代可建营垒</t>
+          <t>土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；城堡科技树 16/21。缺：囤积、强化城墙、箭孔、开垛口、炮塔</t>
+          <t>原生条目 1 条（强 1）；城堡科技树 17/21。缺：工兵、建筑学、开垛口、炮塔</t>
         </is>
       </c>
     </row>
@@ -3691,22 +3699,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17/21</t>
+          <t>16/21</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%</t>
+          <t>城堡时代可建营垒</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；城堡科技树 17/21。缺：建筑学、强化城墙、开垛口、炮塔</t>
+          <t>原生条目 2 条（强 1）；城堡科技树 16/21。缺：囤积、强化城墙、箭孔、开垛口、炮塔</t>
         </is>
       </c>
     </row>
@@ -3716,22 +3724,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15/21</t>
+          <t>17/21</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；城堡科技树 15/21。缺：强化城墙、箭孔、开垛口、炮塔、攻城工程技师</t>
+          <t>原生条目 3 条（强 2）；城堡科技树 17/21。缺：建筑学、强化城墙、开垛口、炮塔</t>
         </is>
       </c>
     </row>
@@ -3741,22 +3749,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12/21</t>
+          <t>15/21</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；城堡科技树 12/21。缺：工兵、建筑学、箭孔、开垛口、弹道学</t>
+          <t>原生条目 1 条（强 1）；城堡科技树 15/21。缺：强化城墙、箭孔、开垛口、炮塔、攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -3766,22 +3774,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14/21</t>
+          <t>12/21</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
+          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；城堡科技树 14/21。缺：砖石建筑、建筑学、强化城墙、开垛口、炮塔</t>
+          <t>原生条目 1 条（强 1）；城堡科技树 12/21。缺：工兵、建筑学、箭孔、开垛口、弹道学</t>
         </is>
       </c>
     </row>
@@ -3791,22 +3799,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11/21</t>
+          <t>14/21</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；城堡科技树 11/21。缺：工兵、砖石建筑、建筑学、强化城墙、箭孔</t>
+          <t>原生条目 2 条（强 2）；城堡科技树 14/21。缺：砖石建筑、建筑学、强化城墙、开垛口、炮塔</t>
         </is>
       </c>
     </row>
@@ -3816,22 +3824,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14/21</t>
+          <t>11/21</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>任何高地可建除TC外所有建筑；堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 4）；城堡科技树 14/21。缺：工兵、开垛口、弹道学、灼热箭、化学</t>
+          <t>原生条目 1 条（强 1）；城堡科技树 11/21。缺：工兵、砖石建筑、建筑学、强化城墙、箭孔</t>
         </is>
       </c>
     </row>
@@ -3841,47 +3849,47 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17/21</t>
+          <t>14/21</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>敌方城堡始终可见；布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>任何高地可建除TC外所有建筑；堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；城堡科技树 17/21。缺：强化城墙、开垛口、灼热箭、护腕</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+          <t>原生条目 1 条（强 4）；城堡科技树 14/21。缺：工兵、开垛口、弹道学、灼热箭、化学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>18/21</t>
+          <t>17/21</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>建筑石料-15%</t>
+          <t>敌方城堡始终可见；布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；城堡科技树 18/21。缺：建筑学、开垛口、炮塔</t>
+          <t>原生条目 2 条（强 2）；城堡科技树 17/21。缺：强化城墙、开垛口、灼热箭、护腕</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4060,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>高海拔单位和建筑受伤-15%；斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
+          <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -4091,7 +4099,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -4112,7 +4120,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>城堡可用攻城工程技师；攻城/防御工事升级木材-75%，研究+100%；加固堡垒（防御工事每分钟回500生命）</t>
+          <t>城堡可用攻城工程技师；加固堡垒（防御工事每分钟回500生命）</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -4127,7 +4135,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4142,12 +4150,12 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>城堡时代可建营垒</t>
+          <t>土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4165,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4172,22 +4180,22 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%；初始石料+100</t>
+          <t>城堡时代可建营垒</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；城堡科技树 16/21；缺 囤积、强化城墙、箭孔、开垛口；最直接一条：城堡时代可建营垒</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -4202,12 +4210,12 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；城堡科技树 17/21；缺 建筑学、强化城墙、开垛口、炮塔；最直接一条：黑暗可建城楼（替瞭望塔系）</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4225,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4232,12 +4240,12 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 12/21；缺 工兵、建筑学、箭孔、开垛口；最直接一条：斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 15/21；缺 强化城墙、箭孔、开垛口、炮塔；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4255,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4262,12 +4270,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
+          <t>斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 砖石建筑、建筑学、强化城墙、开垛口；最直接一条：箭毒（步弓手/防御工事造成中毒伤害）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 12/21；缺 工兵、建筑学、箭孔、开垛口；最直接一条：斯坎达瓦拉斯堡垒（堡垒可用炮台升级）</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4285,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4292,12 +4300,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 11/21；缺 工兵、砖石建筑、建筑学、强化城墙；最直接一条：伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 砖石建筑、建筑学、强化城墙、开垛口；最直接一条：箭毒（步弓手/防御工事造成中毒伤害）</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4315,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4322,12 +4330,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>任何高地可建除TC外所有建筑；迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）；建筑的视野 +3</t>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 4 / 弱 0）；城堡科技树 14/21；缺 工兵、开垛口、弹道学、灼热箭；最直接一条：任何高地可建除TC外所有建筑</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；城堡科技树 11/21；缺 工兵、砖石建筑、建筑学、强化城墙；最直接一条：伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4345,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4352,12 +4360,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>敌方城堡始终可见</t>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点；任何高地可建除TC外所有建筑</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 17/21；缺 强化城墙、开垛口、灼热箭、护腕；最直接一条：敌方城堡始终可见</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 4 / 弱 0）；城堡科技树 14/21；缺 工兵、开垛口、弹道学、灼热箭；最直接一条：任何高地可建除TC外所有建筑</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4375,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4382,12 +4390,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>建筑石料-15%</t>
+          <t>敌方城堡始终可见</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；城堡科技树 18/21；缺 建筑学、开垛口、炮塔；最直接一条：建筑石料-15%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；城堡科技树 17/21；缺 强化城墙、开垛口、灼热箭、护腕；最直接一条：敌方城堡始终可见</t>
         </is>
       </c>
     </row>
@@ -4421,13 +4429,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -4442,12 +4450,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>哨站视野 +3 且不消耗石料</t>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；城堡科技树 17/21；缺 囤积、箭孔、开垛口、炮塔</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 14/21；缺 建筑学、箭孔、开垛口、灼热箭；最直接一条：罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4465,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4472,22 +4480,22 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 4 条（强 2 / 弱 0）；城堡科技树 14/21；缺 建筑学、箭孔、开垛口、灼热箭；最直接一条：罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="51" customHeight="1">
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 13/21；缺 建筑学、强化城墙、箭孔、开垛口；最直接一条：库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -4502,12 +4510,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
+          <t>城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 13/21；缺 建筑学、强化城墙、箭孔、开垛口；最直接一条：库曼雇佣军（团队每人每座城堡免费训5精锐钦察）</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 16/21；缺 开垛口、灼热箭、炮塔、护腕；最直接一条：城堡城堡/帝王费用-15/25%</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4525,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -4532,12 +4540,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>城堡城堡/帝王费用-15/25%</t>
+          <t>城堡起TC木材费用-50%</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；城堡科技树 16/21；缺 开垛口、灼热箭、炮塔、护腕；最直接一条：城堡城堡/帝王费用-15/25%</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4555,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -4562,12 +4570,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>城墙费用 -50%</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；城堡科技树 17/21；缺 箭孔、开垛口、炮塔、攻城工程技师</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 囤积、箭孔、开垛口</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4585,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -4592,12 +4600,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>城堡起TC木材费用-50%</t>
+          <t>城墙费用 -50%</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 开垛口、炮塔、采石场</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；城堡科技树 17/21；缺 箭孔、开垛口、炮塔、攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4615,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -4622,12 +4630,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>建筑石料-15%</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；城堡科技树 18/21；缺 囤积、箭孔、开垛口</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 1）；城堡科技树 18/21；缺 建筑学、开垛口、炮塔；最直接一条：建筑石料-15%</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4645,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -4652,12 +4660,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>土堡（团队城堡工作速度+25%）</t>
+          <t>建筑木材-15%</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；城堡科技树 17/21；缺 工兵、建筑学、开垛口、炮塔；最直接一条：土堡（团队城堡工作速度+25%）</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 1）；城堡科技树 16/21；缺 箭孔、开垛口、炮塔、攻城工程技师；最直接一条：建筑木材-15%</t>
         </is>
       </c>
     </row>
@@ -4667,27 +4675,27 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强城堡</t>
+          <t>哨站视野 +3 且不消耗石料</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>阶段3·资源效率；原生条目 1 条（强 0 / 弱 1）；城堡科技树 17/21；缺 囤积、箭孔、开垛口、炮塔</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4705,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -4717,7 +4725,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4735,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -4747,7 +4755,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4765,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -4777,7 +4785,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4795,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -4807,7 +4815,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4825,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -4837,7 +4845,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4855,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -4867,7 +4875,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4885,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -4897,7 +4905,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4915,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -4927,7 +4935,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4945,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -4957,7 +4965,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4975,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -4987,7 +4995,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -4997,7 +5005,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -5017,7 +5025,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5035,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -5047,7 +5055,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5065,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -5077,7 +5085,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于城堡。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
